--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_h_9.xlsx
@@ -658,7 +658,7 @@
         <v>0.008452235047349248</v>
       </c>
       <c r="C2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>39798568</v>
+        <v>4024169</v>
       </c>
       <c r="L2" t="n">
-        <v>21827250</v>
+        <v>1844144</v>
       </c>
       <c r="M2" t="n">
-        <v>5163616</v>
+        <v>367135</v>
       </c>
       <c r="N2" t="n">
-        <v>235344</v>
+        <v>7579</v>
       </c>
       <c r="O2" t="n">
-        <v>3046073</v>
+        <v>202254</v>
       </c>
       <c r="P2" t="n">
-        <v>1190464</v>
+        <v>67680</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999305009841919</v>
+        <v>0.9999915957450867</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8582013845443726</v>
+        <v>0.7545484304428101</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7364888787269592</v>
+        <v>0.5706203579902649</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6756995916366577</v>
+        <v>0.4492723047733307</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2772905826568604</v>
+        <v>0.060257438570261</v>
       </c>
       <c r="V2" t="n">
-        <v>0.725345253944397</v>
+        <v>0.4976918399333954</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8242697715759277</v>
+        <v>0.6622762680053711</v>
       </c>
       <c r="X2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>43199395</v>
+        <v>4763805</v>
       </c>
       <c r="AG2" t="n">
-        <v>26831006</v>
+        <v>3006353</v>
       </c>
       <c r="AH2" t="n">
-        <v>7210544</v>
+        <v>805109</v>
       </c>
       <c r="AI2" t="n">
-        <v>531451</v>
+        <v>59219</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4136352</v>
+        <v>460827</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560797214508057</v>
+        <v>0.9549221992492676</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9115321636199951</v>
+        <v>0.912146270275116</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582335114479065</v>
+        <v>0.8583800792694092</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6618483662605286</v>
+        <v>0.6608968377113342</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020155668258667</v>
+        <v>0.9020029902458191</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314467906951904</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002026323576521127</v>
       </c>
       <c r="C3" t="n">
-        <v>2766</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>39798568</v>
+        <v>4024169</v>
       </c>
       <c r="E3" t="n">
-        <v>5172395</v>
+        <v>910466</v>
       </c>
       <c r="F3" t="n">
-        <v>123519</v>
+        <v>36362</v>
       </c>
       <c r="G3" t="n">
-        <v>10646</v>
+        <v>2403</v>
       </c>
       <c r="H3" t="n">
-        <v>7308</v>
+        <v>2091</v>
       </c>
       <c r="I3" t="n">
-        <v>426</v>
+        <v>151</v>
       </c>
       <c r="J3" t="n">
-        <v>90145650</v>
+        <v>10016569</v>
       </c>
       <c r="K3" t="n">
-        <v>95274947</v>
+        <v>10044899</v>
       </c>
       <c r="L3" t="n">
-        <v>109666558</v>
+        <v>11635597</v>
       </c>
       <c r="M3" t="n">
-        <v>136077438</v>
+        <v>14939679</v>
       </c>
       <c r="N3" t="n">
-        <v>145549261</v>
+        <v>16121705</v>
       </c>
       <c r="O3" t="n">
-        <v>141224472</v>
+        <v>15614089</v>
       </c>
       <c r="P3" t="n">
-        <v>144971791</v>
+        <v>16101401</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8821459412574768</v>
+        <v>0.8087717294692993</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7401529550552368</v>
+        <v>0.557762622833252</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6139343976974487</v>
+        <v>0.3906194269657135</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2928052842617035</v>
+        <v>0.08449558168649673</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6638463735580444</v>
+        <v>0.3955055177211761</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6838571429252625</v>
+        <v>0.3494315445423126</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43199395</v>
+        <v>4763805</v>
       </c>
       <c r="Z3" t="n">
-        <v>1777968</v>
+        <v>196543</v>
       </c>
       <c r="AA3" t="n">
-        <v>76428</v>
+        <v>8427</v>
       </c>
       <c r="AB3" t="n">
-        <v>61298</v>
+        <v>6839</v>
       </c>
       <c r="AC3" t="n">
-        <v>269</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>90149598</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>99866284</v>
+        <v>11129066</v>
       </c>
       <c r="AG3" t="n">
-        <v>114872156</v>
+        <v>12733718</v>
       </c>
       <c r="AH3" t="n">
-        <v>137364636</v>
+        <v>15256890</v>
       </c>
       <c r="AI3" t="n">
-        <v>145891115</v>
+        <v>16209518</v>
       </c>
       <c r="AJ3" t="n">
-        <v>141928554</v>
+        <v>15768153</v>
       </c>
       <c r="AK3" t="n">
-        <v>145106283</v>
+        <v>16122647</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575262069702148</v>
+        <v>0.95742267370224</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.909828245639801</v>
+        <v>0.9092735648155212</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573063611984253</v>
+        <v>0.8566092252731323</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6612093448638916</v>
+        <v>0.6602116227149963</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014564752578735</v>
+        <v>0.9011421799659729</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312204718589783</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03197108341586186</v>
       </c>
       <c r="C4" t="n">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>6124023</v>
+        <v>1196577</v>
       </c>
       <c r="E4" t="n">
-        <v>21827250</v>
+        <v>1844144</v>
       </c>
       <c r="F4" t="n">
-        <v>1327745</v>
+        <v>217831</v>
       </c>
       <c r="G4" t="n">
-        <v>72680</v>
+        <v>16967</v>
       </c>
       <c r="H4" t="n">
-        <v>126044</v>
+        <v>27865</v>
       </c>
       <c r="I4" t="n">
-        <v>12344</v>
+        <v>2926</v>
       </c>
       <c r="J4" t="n">
-        <v>3948</v>
+        <v>53</v>
       </c>
       <c r="K4" t="n">
-        <v>6575825</v>
+        <v>1309046</v>
       </c>
       <c r="L4" t="n">
-        <v>7809654</v>
+        <v>1387679</v>
       </c>
       <c r="M4" t="n">
-        <v>2478265</v>
+        <v>450042</v>
       </c>
       <c r="N4" t="n">
-        <v>613383</v>
+        <v>118198</v>
       </c>
       <c r="O4" t="n">
-        <v>1153407</v>
+        <v>204130</v>
       </c>
       <c r="P4" t="n">
-        <v>253801</v>
+        <v>34513</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999652504920959</v>
+        <v>0.9999957680702209</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8700088858604431</v>
+        <v>0.7807197570800781</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7383162975311279</v>
+        <v>0.5641182661056519</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6433379054069519</v>
+        <v>0.4178978800773621</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2848368287086487</v>
+        <v>0.07034723460674286</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6932345628738403</v>
+        <v>0.4407533705234528</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7475269436836243</v>
+        <v>0.4574843049049377</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1853220</v>
+        <v>210159</v>
       </c>
       <c r="Z4" t="n">
-        <v>26831006</v>
+        <v>3006353</v>
       </c>
       <c r="AA4" t="n">
-        <v>745446</v>
+        <v>83023</v>
       </c>
       <c r="AB4" t="n">
-        <v>49654</v>
+        <v>5590</v>
       </c>
       <c r="AC4" t="n">
-        <v>10250</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1984488</v>
+        <v>224879</v>
       </c>
       <c r="AG4" t="n">
-        <v>2604056</v>
+        <v>289558</v>
       </c>
       <c r="AH4" t="n">
-        <v>1191067</v>
+        <v>132831</v>
       </c>
       <c r="AI4" t="n">
-        <v>271529</v>
+        <v>30385</v>
       </c>
       <c r="AJ4" t="n">
-        <v>449325</v>
+        <v>50066</v>
       </c>
       <c r="AK4" t="n">
-        <v>119309</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568024277687073</v>
+        <v>0.9561707377433777</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106794595718384</v>
+        <v>0.9107076525688171</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577696084976196</v>
+        <v>0.8574937582015991</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6615287065505981</v>
+        <v>0.660554051399231</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017359018325806</v>
+        <v>0.9015724062919617</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931333601474762</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>623</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>314634</v>
+        <v>83087</v>
       </c>
       <c r="E5" t="n">
-        <v>2188199</v>
+        <v>374274</v>
       </c>
       <c r="F5" t="n">
-        <v>5163616</v>
+        <v>367135</v>
       </c>
       <c r="G5" t="n">
-        <v>195307</v>
+        <v>32751</v>
       </c>
       <c r="H5" t="n">
-        <v>498188</v>
+        <v>73399</v>
       </c>
       <c r="I5" t="n">
-        <v>50130</v>
+        <v>9225</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5317060</v>
+        <v>951486</v>
       </c>
       <c r="L5" t="n">
-        <v>7662938</v>
+        <v>1462180</v>
       </c>
       <c r="M5" t="n">
-        <v>3247081</v>
+        <v>572744</v>
       </c>
       <c r="N5" t="n">
-        <v>568412</v>
+        <v>82118</v>
       </c>
       <c r="O5" t="n">
-        <v>1542448</v>
+        <v>309127</v>
       </c>
       <c r="P5" t="n">
-        <v>550344</v>
+        <v>126006</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999731183052063</v>
+        <v>0.9999967813491821</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9190775156021118</v>
+        <v>0.8615684509277344</v>
       </c>
       <c r="S5" t="n">
-        <v>0.894720196723938</v>
+        <v>0.8254789710044861</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9610431790351868</v>
+        <v>0.9373661279678345</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9919587373733521</v>
+        <v>0.9877329468727112</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9816566705703735</v>
+        <v>0.9685689210891724</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9945283532142639</v>
+        <v>0.9901700615882874</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>72334</v>
+        <v>8098</v>
       </c>
       <c r="Z5" t="n">
-        <v>769884</v>
+        <v>86770</v>
       </c>
       <c r="AA5" t="n">
-        <v>7210544</v>
+        <v>805109</v>
       </c>
       <c r="AB5" t="n">
-        <v>89719</v>
+        <v>10018</v>
       </c>
       <c r="AC5" t="n">
-        <v>262519</v>
+        <v>29251</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1916233</v>
+        <v>211850</v>
       </c>
       <c r="AG5" t="n">
-        <v>2659182</v>
+        <v>299971</v>
       </c>
       <c r="AH5" t="n">
-        <v>1200153</v>
+        <v>134770</v>
       </c>
       <c r="AI5" t="n">
-        <v>272305</v>
+        <v>30478</v>
       </c>
       <c r="AJ5" t="n">
-        <v>452169</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119732</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734584093093872</v>
+        <v>0.9732553958892822</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641875028610229</v>
+        <v>0.9638981223106384</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837294816970825</v>
+        <v>0.9836125373840332</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962996244430542</v>
+        <v>0.99627286195755</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.993865966796875</v>
+        <v>0.9938381910324097</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983735084533691</v>
+        <v>0.9983692169189453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>217</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>116185</v>
+        <v>20195</v>
       </c>
       <c r="E6" t="n">
-        <v>167752</v>
+        <v>24762</v>
       </c>
       <c r="F6" t="n">
-        <v>199200</v>
+        <v>27727</v>
       </c>
       <c r="G6" t="n">
-        <v>235344</v>
+        <v>7579</v>
       </c>
       <c r="H6" t="n">
-        <v>77319</v>
+        <v>8395</v>
       </c>
       <c r="I6" t="n">
-        <v>7739</v>
+        <v>1028</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58491</v>
+        <v>6586</v>
       </c>
       <c r="Z6" t="n">
-        <v>48185</v>
+        <v>5354</v>
       </c>
       <c r="AA6" t="n">
-        <v>98390</v>
+        <v>11038</v>
       </c>
       <c r="AB6" t="n">
-        <v>531451</v>
+        <v>59219</v>
       </c>
       <c r="AC6" t="n">
-        <v>62910</v>
+        <v>7019</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>20178</v>
+        <v>8877</v>
       </c>
       <c r="E7" t="n">
-        <v>259824</v>
+        <v>70752</v>
       </c>
       <c r="F7" t="n">
-        <v>774933</v>
+        <v>151638</v>
       </c>
       <c r="G7" t="n">
-        <v>304300</v>
+        <v>56673</v>
       </c>
       <c r="H7" t="n">
-        <v>3046073</v>
+        <v>202254</v>
       </c>
       <c r="I7" t="n">
-        <v>183162</v>
+        <v>21183</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7290</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>267822</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68465</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4136352</v>
+        <v>460827</v>
       </c>
       <c r="AD7" t="n">
-        <v>108401</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>189</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>805</v>
+        <v>310</v>
       </c>
       <c r="E8" t="n">
-        <v>21484</v>
+        <v>7425</v>
       </c>
       <c r="F8" t="n">
-        <v>52868</v>
+        <v>16484</v>
       </c>
       <c r="G8" t="n">
-        <v>30450</v>
+        <v>9404</v>
       </c>
       <c r="H8" t="n">
-        <v>444548</v>
+        <v>92380</v>
       </c>
       <c r="I8" t="n">
-        <v>1190464</v>
+        <v>67680</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2981</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2393</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113377</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
